--- a/Data/National Accounts/PSA-16IAC_2018PSNA_Ann.xlsx
+++ b/Data/National Accounts/PSA-16IAC_2018PSNA_Ann.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Annl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Annl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC553BD-3B70-4055-98D8-7A932FC5F6BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED9CCF5-1D11-4D4A-A660-92486525F661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IAC" sheetId="1" r:id="rId1"/>
@@ -611,9 +611,6 @@
     <t>2023 - 2024</t>
   </si>
   <si>
-    <t>As of January 2026</t>
-  </si>
-  <si>
     <t>Annual 2000 to 2025</t>
   </si>
   <si>
@@ -621,6 +618,9 @@
   </si>
   <si>
     <t>2024 - 2025</t>
+  </si>
+  <si>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -23616,7 +23616,7 @@
     </row>
     <row r="3" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -23627,7 +23627,7 @@
     </row>
     <row r="6" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -23883,10 +23883,10 @@
         <v>59954.337014939723</v>
       </c>
       <c r="Z12" s="9">
-        <v>63006.127753822693</v>
+        <v>64156.992108568666</v>
       </c>
       <c r="AA12" s="9">
-        <v>68673.852584199427</v>
+        <v>70588.602194755382</v>
       </c>
       <c r="AB12" s="10"/>
       <c r="AC12" s="10"/>
@@ -24035,10 +24035,10 @@
         <v>672506.45679512247</v>
       </c>
       <c r="Z13" s="13">
-        <v>705816.61618459702</v>
+        <v>706162.22127093899</v>
       </c>
       <c r="AA13" s="13">
-        <v>731682.56641384808</v>
+        <v>734779.19255478552</v>
       </c>
       <c r="AB13" s="10"/>
       <c r="AC13" s="10"/>
@@ -24285,10 +24285,10 @@
         <v>732460.79381006223</v>
       </c>
       <c r="Z15" s="15">
-        <v>768822.74393841974</v>
+        <v>770319.21337950765</v>
       </c>
       <c r="AA15" s="15">
-        <v>800356.41899804748</v>
+        <v>805367.79474954086</v>
       </c>
       <c r="AB15" s="10"/>
       <c r="AC15" s="10"/>
@@ -24602,7 +24602,7 @@
     </row>
     <row r="22" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -24613,7 +24613,7 @@
     </row>
     <row r="25" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -24869,10 +24869,10 @@
         <v>54228.896276115578</v>
       </c>
       <c r="Z31" s="9">
-        <v>56216.443451053492</v>
+        <v>57238.112781540171</v>
       </c>
       <c r="AA31" s="9">
-        <v>60911.90364094876</v>
+        <v>62523.498476195397</v>
       </c>
       <c r="AB31" s="10"/>
       <c r="AC31" s="10"/>
@@ -25021,10 +25021,10 @@
         <v>664473.60849740729</v>
       </c>
       <c r="Z32" s="13">
-        <v>694857.10201809986</v>
+        <v>695191.14036616345</v>
       </c>
       <c r="AA32" s="13">
-        <v>716990.62203968735</v>
+        <v>719936.7557895442</v>
       </c>
       <c r="AB32" s="10"/>
       <c r="AC32" s="10"/>
@@ -25271,10 +25271,10 @@
         <v>718702.50477352284</v>
       </c>
       <c r="Z34" s="15">
-        <v>751073.54546915332</v>
+        <v>752429.2531477036</v>
       </c>
       <c r="AA34" s="15">
-        <v>777902.52568063606</v>
+        <v>782460.25426573958</v>
       </c>
       <c r="AB34" s="10"/>
       <c r="AC34" s="10"/>
@@ -25588,7 +25588,7 @@
     </row>
     <row r="41" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -25599,7 +25599,7 @@
     </row>
     <row r="44" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -25716,7 +25716,7 @@
         <v>46</v>
       </c>
       <c r="Z48" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA48" s="20"/>
     </row>
@@ -25797,10 +25797,10 @@
         <v>4.377523485919113</v>
       </c>
       <c r="Y50" s="21">
-        <v>5.090191787330582</v>
+        <v>7.0097599320991577</v>
       </c>
       <c r="Z50" s="21">
-        <v>8.9955136626101506</v>
+        <v>10.024799908485306</v>
       </c>
       <c r="AA50" s="21"/>
       <c r="AB50" s="10"/>
@@ -25942,10 +25942,10 @@
         <v>5.3125062937681662</v>
       </c>
       <c r="Y51" s="21">
-        <v>4.9531359963763748</v>
+        <v>5.0045265938717449</v>
       </c>
       <c r="Z51" s="21">
-        <v>3.6646842304554355</v>
+        <v>4.0524642103258088</v>
       </c>
       <c r="AA51" s="21"/>
       <c r="AB51" s="10"/>
@@ -26180,10 +26180,10 @@
         <v>5.2353458900458207</v>
       </c>
       <c r="Y53" s="21">
-        <v>4.9643544658837726</v>
+        <v>5.1686615706099843</v>
       </c>
       <c r="Z53" s="21">
-        <v>4.1015533565111895</v>
+        <v>4.549877604151888</v>
       </c>
       <c r="AA53" s="21"/>
       <c r="AB53" s="10"/>
@@ -26483,7 +26483,7 @@
     </row>
     <row r="60" spans="1:91" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:91" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -26494,7 +26494,7 @@
     </row>
     <row r="63" spans="1:91" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:91" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -26611,7 +26611,7 @@
         <v>46</v>
       </c>
       <c r="Z67" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA67" s="7"/>
     </row>
@@ -26692,10 +26692,10 @@
         <v>-1.2830572653192291</v>
       </c>
       <c r="Y69" s="21">
-        <v>3.6651071871682177</v>
+        <v>5.549101516104372</v>
       </c>
       <c r="Z69" s="21">
-        <v>8.3524675373381001</v>
+        <v>9.2340320772417357</v>
       </c>
       <c r="AA69" s="21"/>
       <c r="AB69" s="10"/>
@@ -26837,10 +26837,10 @@
         <v>4.6187492725122894</v>
       </c>
       <c r="Y70" s="21">
-        <v>4.5725658825486875</v>
+        <v>4.6228370060051844</v>
       </c>
       <c r="Z70" s="21">
-        <v>3.1853340718982679</v>
+        <v>3.5595412522586116</v>
       </c>
       <c r="AA70" s="21"/>
       <c r="AB70" s="10"/>
@@ -27075,10 +27075,10 @@
         <v>4.1489312237728484</v>
       </c>
       <c r="Y72" s="21">
-        <v>4.5040945983388667</v>
+        <v>4.6927272619995648</v>
       </c>
       <c r="Z72" s="21">
-        <v>3.5720843016410839</v>
+        <v>3.9912059495832466</v>
       </c>
       <c r="AA72" s="21"/>
       <c r="AB72" s="10"/>
@@ -27374,7 +27374,7 @@
     </row>
     <row r="78" spans="1:92" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79" spans="1:92" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -27385,7 +27385,7 @@
     </row>
     <row r="81" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="82" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -27588,10 +27588,10 @@
         <v>110.55791493463576</v>
       </c>
       <c r="Z87" s="21">
-        <v>112.07775498761467</v>
+        <v>112.08788863014347</v>
       </c>
       <c r="AA87" s="21">
-        <v>112.74290980791577</v>
+        <v>112.89931612133095</v>
       </c>
       <c r="AB87" s="10"/>
       <c r="AC87" s="10"/>
@@ -27740,10 +27740,10 @@
         <v>101.20890403997838</v>
       </c>
       <c r="Z88" s="21">
-        <v>101.57723280580527</v>
+        <v>101.57813876900057</v>
       </c>
       <c r="AA88" s="21">
-        <v>102.04911248802185</v>
+        <v>102.06163064267552</v>
       </c>
       <c r="AB88" s="10"/>
       <c r="AC88" s="10"/>
@@ -27990,10 +27990,10 @@
         <v>101.91432323460106</v>
       </c>
       <c r="Z90" s="21">
-        <v>102.36317715839391</v>
+        <v>102.37762688744003</v>
       </c>
       <c r="AA90" s="21">
-        <v>102.88646618003523</v>
+        <v>102.92762991588597</v>
       </c>
       <c r="AB90" s="10"/>
       <c r="AC90" s="10"/>
@@ -28111,7 +28111,7 @@
     </row>
     <row r="97" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="98" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -28122,7 +28122,7 @@
     </row>
     <row r="100" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="101" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -28325,10 +28325,10 @@
         <v>8.1853305353141899</v>
       </c>
       <c r="Z106" s="21">
-        <v>8.1951435816094023</v>
+        <v>8.3286241592108503</v>
       </c>
       <c r="AA106" s="21">
-        <v>8.5804087971420344</v>
+        <v>8.7647659435783059</v>
       </c>
       <c r="AB106" s="10"/>
       <c r="AC106" s="10"/>
@@ -28477,10 +28477,10 @@
         <v>91.814669464685807</v>
       </c>
       <c r="Z107" s="21">
-        <v>91.804856418390585</v>
+        <v>91.671375840789153</v>
       </c>
       <c r="AA107" s="21">
-        <v>91.419591202857958</v>
+        <v>91.235234056421703</v>
       </c>
       <c r="AB107" s="10"/>
       <c r="AC107" s="10"/>
@@ -29044,7 +29044,7 @@
     </row>
     <row r="116" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="117" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -29055,7 +29055,7 @@
     </row>
     <row r="119" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="120" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -29258,10 +29258,10 @@
         <v>7.5453885183277825</v>
       </c>
       <c r="Z125" s="21">
-        <v>7.4848120786810899</v>
+        <v>7.6071089131756811</v>
       </c>
       <c r="AA125" s="21">
-        <v>7.8302745691245939</v>
+        <v>7.9906293176344692</v>
       </c>
       <c r="AB125" s="10"/>
       <c r="AC125" s="10"/>
@@ -29410,10 +29410,10 @@
         <v>92.454611481672217</v>
       </c>
       <c r="Z126" s="21">
-        <v>92.515187921318926</v>
+        <v>92.392891086824321</v>
       </c>
       <c r="AA126" s="21">
-        <v>92.169725430875417</v>
+        <v>92.009370682365528</v>
       </c>
       <c r="AB126" s="10"/>
       <c r="AC126" s="10"/>
